--- a/artfynd/A 1025-2026 artfynd.xlsx
+++ b/artfynd/A 1025-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>582179</v>
+        <v>920736</v>
       </c>
       <c r="B2" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,26 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2059</v>
+        <v>1962</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>870682.4871302098</v>
+        <v>870528</v>
       </c>
       <c r="R2" t="n">
-        <v>7496703.118303907</v>
+        <v>7496584</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,19 +752,9 @@
           <t>2009-09-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2009-09-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,42 +786,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1045642</v>
+        <v>84936</v>
       </c>
       <c r="B3" t="n">
-        <v>90639</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3100</v>
+        <v>65</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -850,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>871222.1953724057</v>
+        <v>870704</v>
       </c>
       <c r="R3" t="n">
-        <v>7496344.006481961</v>
+        <v>7496590</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,19 +863,9 @@
           <t>2009-09-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2009-09-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,15 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>292872</v>
+        <v>292865</v>
       </c>
       <c r="B4" t="n">
-        <v>90641</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -962,7 +927,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -976,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>870873.4568414363</v>
+        <v>870697</v>
       </c>
       <c r="R4" t="n">
-        <v>7496694.443446574</v>
+        <v>7496678</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,19 +974,9 @@
           <t>2009-09-09</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2009-09-09</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,15 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>292870</v>
+        <v>292869</v>
       </c>
       <c r="B5" t="n">
-        <v>90641</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,7 +1038,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1102,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>870817.7328779981</v>
+        <v>870689</v>
       </c>
       <c r="R5" t="n">
-        <v>7496757.604299911</v>
+        <v>7496607</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1135,19 +1085,9 @@
           <t>2009-09-09</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2009-09-09</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1179,15 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>292869</v>
+        <v>292870</v>
       </c>
       <c r="B6" t="n">
-        <v>90641</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1214,7 +1149,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1228,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>870688.967394428</v>
+        <v>870818</v>
       </c>
       <c r="R6" t="n">
-        <v>7496606.906320823</v>
+        <v>7496758</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1261,19 +1196,9 @@
           <t>2009-09-09</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2009-09-09</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1305,42 +1230,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1045636</v>
+        <v>292871</v>
       </c>
       <c r="B7" t="n">
-        <v>90639</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3100</v>
+        <v>149</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1354,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>870848.1620029879</v>
+        <v>870682</v>
       </c>
       <c r="R7" t="n">
-        <v>7496791.131241909</v>
+        <v>7496624</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1387,21 +1307,11 @@
           <t>2009-09-09</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2009-09-09</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1413,7 +1323,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Sandtallskog</t>
+          <t>Sandtalskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1431,15 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>292871</v>
+        <v>292872</v>
       </c>
       <c r="B8" t="n">
-        <v>90641</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1371,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1480,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>870681.5193836107</v>
+        <v>870873</v>
       </c>
       <c r="R8" t="n">
-        <v>7496623.803080024</v>
+        <v>7496694</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1513,21 +1418,11 @@
           <t>2009-09-09</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2009-09-09</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1539,7 +1434,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Sandtalskog</t>
+          <t>Sandtallskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1557,15 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1045641</v>
+        <v>920735</v>
       </c>
       <c r="B9" t="n">
-        <v>90639</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,26 +1463,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3100</v>
+        <v>1962</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1606,10 +1496,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>870970.830546224</v>
+        <v>870706</v>
       </c>
       <c r="R9" t="n">
-        <v>7496690.571246817</v>
+        <v>7496377</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1639,19 +1529,9 @@
           <t>2009-09-09</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2009-09-09</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1683,42 +1563,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1045639</v>
+        <v>582179</v>
       </c>
       <c r="B10" t="n">
-        <v>90639</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3100</v>
+        <v>2059</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1732,10 +1607,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>870716.7695363122</v>
+        <v>870682</v>
       </c>
       <c r="R10" t="n">
-        <v>7496767.607513326</v>
+        <v>7496703</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1765,21 +1640,11 @@
           <t>2009-09-09</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2009-09-09</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1791,7 +1656,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Sandtalskog</t>
+          <t>Sandtallskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1809,42 +1674,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>84936</v>
+        <v>1045636</v>
       </c>
       <c r="B11" t="n">
-        <v>89633</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>65</v>
+        <v>3100</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1858,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>870703.7979786841</v>
+        <v>870848</v>
       </c>
       <c r="R11" t="n">
-        <v>7496590.26585705</v>
+        <v>7496791</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1891,19 +1751,9 @@
           <t>2009-09-09</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2009-09-09</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1935,15 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>920735</v>
+        <v>1045637</v>
       </c>
       <c r="B12" t="n">
-        <v>88476</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1951,21 +1796,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1962</v>
+        <v>3100</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1984,10 +1829,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>870705.6053543682</v>
+        <v>870706</v>
       </c>
       <c r="R12" t="n">
-        <v>7496377.14999921</v>
+        <v>7496702</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2017,19 +1862,9 @@
           <t>2009-09-09</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2009-09-09</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2061,42 +1896,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>6536536</v>
+        <v>1045639</v>
       </c>
       <c r="B13" t="n">
-        <v>88030</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>245044</v>
+        <v>3100</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallmusseron</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tricholoma roseoacerbum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>A.Riva</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2110,10 +1940,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>870855.8122192021</v>
+        <v>870717</v>
       </c>
       <c r="R13" t="n">
-        <v>7496767.243484953</v>
+        <v>7496768</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2143,24 +1973,9 @@
           <t>2009-09-09</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2009-09-09</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Tallmusseron</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2189,6 +2004,344 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1045641</v>
+      </c>
+      <c r="B14" t="n">
+        <v>93222</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>3100</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Talltaggsvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Phellodon fuligineoalbus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(J.C.Schmidt) Baird</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Saari Koskenvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>870971</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7496691</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2009-09-09</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2009-09-09</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1045642</v>
+      </c>
+      <c r="B15" t="n">
+        <v>93222</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>3100</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Talltaggsvamp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Phellodon fuligineoalbus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(J.C.Schmidt) Baird</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Saari Koskenvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>871222</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7496344</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2009-09-09</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2009-09-09</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>6536536</v>
+      </c>
+      <c r="B16" t="n">
+        <v>90699</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>245044</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tallmusseron</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tricholoma roseoacerbum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>A.Riva</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Saari Koskenvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>870856</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7496767</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2009-09-09</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2009-09-09</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Tallmusseron</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Sandtalskog</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1025-2026 artfynd.xlsx
+++ b/artfynd/A 1025-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84936</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/292865</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/292869</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/292871</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/920735</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1338,6 +1368,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/920736</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1449,6 +1484,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/582179</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1560,6 +1600,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1045637</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1671,6 +1716,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1045639</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1782,6 +1832,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/292870</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1893,6 +1948,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/292872</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2004,6 +2064,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1045636</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2115,6 +2180,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1045641</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2226,6 +2296,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1045642</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2342,8 +2417,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6536536</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>